--- a/Decks/Yorion.xlsx
+++ b/Decks/Yorion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D416BDD4-D512-4E1A-8502-ED7BACEE9C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098228ED-5D1B-4ACE-B9B6-1C8C81AF3786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B4381E2-5BD2-4C34-834D-2B6229AFC0E6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="81">
   <si>
     <t>Função</t>
   </si>
@@ -143,9 +143,6 @@
     <t>Reality Shift</t>
   </si>
   <si>
-    <t>Path to Exile</t>
-  </si>
-  <si>
     <t>Avatar's Wrath</t>
   </si>
   <si>
@@ -227,9 +224,6 @@
     <t>Proteus Staff</t>
   </si>
   <si>
-    <t>Dawnbringer Cleric</t>
-  </si>
-  <si>
     <t>Azorius Charm</t>
   </si>
   <si>
@@ -282,6 +276,9 @@
   </si>
   <si>
     <t>Hop to It</t>
+  </si>
+  <si>
+    <t>Perplexing Test</t>
   </si>
 </sst>
 </file>
@@ -1326,10 +1323,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1356,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1403,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D48" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F48"/>
     </row>
@@ -1451,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D51" t="s">
         <v>27</v>
@@ -1515,7 +1512,7 @@
         <v>1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D55" t="s">
         <v>32</v>
@@ -1531,7 +1528,7 @@
         <v>1</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D56" t="s">
         <v>33</v>
@@ -1560,13 +1557,13 @@
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D58" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1578,10 +1575,10 @@
         <v>1</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F59"/>
     </row>
@@ -1594,97 +1591,97 @@
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F60"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D61" t="s">
         <v>38</v>
-      </c>
-      <c r="B61" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D61" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F62"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D63" t="s">
+        <v>40</v>
+      </c>
+      <c r="F63" t="s">
         <v>41</v>
-      </c>
-      <c r="D63" t="s">
-        <v>41</v>
-      </c>
-      <c r="F63" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F64"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>43</v>
+      </c>
+      <c r="B65" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C65" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B65" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="D65" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F65"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" ref="B66:B101" si="1">C66&lt;&gt;D66</f>
@@ -1692,281 +1689,281 @@
       </c>
       <c r="C66" s="4"/>
       <c r="D66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F66"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D67" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F67" s="4"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D68" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F68" s="4"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D69" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B71" s="5" t="b">
         <f>C71&lt;&gt;D71</f>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F71"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D72" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D73" t="s">
         <v>49</v>
-      </c>
-      <c r="B73" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D73" t="s">
-        <v>50</v>
       </c>
       <c r="F73" s="4"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D74" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F74"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D75" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F75"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D76" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F76"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D77" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E77" s="4"/>
       <c r="F77"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D78" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D79" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D80" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E80" s="4"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D81" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F81" s="4"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D82" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F82" s="4"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D83" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F83" s="4"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1974,13 +1971,13 @@
       </c>
       <c r="C84" s="4"/>
       <c r="D84" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F84" s="4"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1988,13 +1985,13 @@
       </c>
       <c r="C85" s="4"/>
       <c r="D85" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2002,12 +1999,12 @@
       </c>
       <c r="C86" s="4"/>
       <c r="D86" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2015,12 +2012,12 @@
       </c>
       <c r="C87" s="4"/>
       <c r="D87" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2028,12 +2025,12 @@
       </c>
       <c r="C88" s="4"/>
       <c r="D88" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2041,12 +2038,12 @@
       </c>
       <c r="C89" s="4"/>
       <c r="D89" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2054,12 +2051,12 @@
       </c>
       <c r="C90" s="4"/>
       <c r="D90" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2067,13 +2064,13 @@
       </c>
       <c r="C91" s="4"/>
       <c r="D91" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F91"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2081,13 +2078,13 @@
       </c>
       <c r="C92" s="4"/>
       <c r="D92" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F92"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2095,131 +2092,131 @@
       </c>
       <c r="C93" s="4"/>
       <c r="D93" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F93"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D94" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D95" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D96" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D97" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G97" s="4"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D98" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G98" s="4"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D99" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D100" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G100" s="4"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Yorion.xlsx
+++ b/Decks/Yorion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098228ED-5D1B-4ACE-B9B6-1C8C81AF3786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B15C73D-8B15-4371-802B-AF43C84367F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B4381E2-5BD2-4C34-834D-2B6229AFC0E6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="71">
   <si>
     <t>Função</t>
   </si>
@@ -95,9 +95,6 @@
     <t>Thought Vessel</t>
   </si>
   <si>
-    <t>Prismatic Lens</t>
-  </si>
-  <si>
     <t>Draw</t>
   </si>
   <si>
@@ -152,9 +149,6 @@
     <t>Blink</t>
   </si>
   <si>
-    <t>Felidar Guardian</t>
-  </si>
-  <si>
     <t>Restoration Angel</t>
   </si>
   <si>
@@ -185,9 +179,6 @@
     <t>Suporte</t>
   </si>
   <si>
-    <t>Virtue of Knowledge // Vantress Visions</t>
-  </si>
-  <si>
     <t>Preston, the Vanisher</t>
   </si>
   <si>
@@ -224,30 +215,12 @@
     <t>Proteus Staff</t>
   </si>
   <si>
-    <t>Azorius Charm</t>
-  </si>
-  <si>
-    <t>Clone</t>
-  </si>
-  <si>
-    <t>Phyrexian Metamorph</t>
-  </si>
-  <si>
-    <t>Mirror Image</t>
-  </si>
-  <si>
     <t>Abdel Adrian, Gorion's Ward</t>
   </si>
   <si>
     <t>Ojutai's Command</t>
   </si>
   <si>
-    <t>Reveillark</t>
-  </si>
-  <si>
-    <t>Return to the Ranks</t>
-  </si>
-  <si>
     <t>Claim Jumper</t>
   </si>
   <si>
@@ -258,9 +231,6 @@
   </si>
   <si>
     <t>Ellyn Harbreeze, Busybody</t>
-  </si>
-  <si>
-    <t>Distinguished Conjurer</t>
   </si>
   <si>
     <t>Skycoach Conductor // All Aboard</t>
@@ -719,7 +689,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B65" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B64" si="0">C3&lt;&gt;D3</f>
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -1245,10 +1215,10 @@
       </c>
       <c r="B38" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s">
         <v>14</v>
@@ -1323,339 +1293,337 @@
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D43" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="D44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B45" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D45" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B46" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F46"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B47" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F47"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B48" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D48" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F48"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B49" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="D49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F49"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F50"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F51"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F52"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>28</v>
+      </c>
+      <c r="B53" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B53" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="D53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F53"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F54"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F55"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F56"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F57"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D58" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F59"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F60"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D61" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B62" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="D62" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F62"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D63" t="s">
-        <v>40</v>
-      </c>
-      <c r="F63" t="s">
-        <v>41</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F63"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D64" t="s">
@@ -1665,558 +1633,572 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>41</v>
+      </c>
+      <c r="B65" s="5" t="b">
+        <f t="shared" ref="B65:B101" si="1">C65&lt;&gt;D65</f>
+        <v>1</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D65" t="s">
         <v>43</v>
-      </c>
-      <c r="B65" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D65" t="s">
-        <v>44</v>
       </c>
       <c r="F65"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B66" s="5" t="b">
-        <f t="shared" ref="B66:B101" si="1">C66&lt;&gt;D66</f>
-        <v>1</v>
-      </c>
-      <c r="C66" s="4"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="D66" t="s">
-        <v>45</v>
-      </c>
-      <c r="F66"/>
+        <v>65</v>
+      </c>
+      <c r="F66" s="4"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="D67" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="F67" s="4"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="D68" t="s">
-        <v>46</v>
-      </c>
-      <c r="F68" s="4"/>
+        <v>62</v>
+      </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D69" t="s">
-        <v>71</v>
+        <v>45</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B70" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C70&lt;&gt;D70</f>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>47</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F70"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B71" s="5" t="b">
-        <f>C71&lt;&gt;D71</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F71"/>
+        <v>66</v>
+      </c>
+      <c r="D71" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D72" t="s">
-        <v>76</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="F72" s="4"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D73" t="s">
-        <v>49</v>
-      </c>
-      <c r="F73" s="4"/>
+        <v>47</v>
+      </c>
+      <c r="F73"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>46</v>
+      </c>
+      <c r="B74" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D74" t="s">
         <v>48</v>
-      </c>
-      <c r="B74" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D74" t="s">
-        <v>50</v>
       </c>
       <c r="F74"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D75" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F75"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B76" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>58</v>
+        <f>C76&lt;&gt;D76</f>
+        <v>0</v>
+      </c>
+      <c r="C76" t="s">
+        <v>40</v>
       </c>
       <c r="D76" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F76"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D77" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E77" s="4"/>
       <c r="F77"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D78" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D79" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D80" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E80" s="4"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D81" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F81" s="4"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D82" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F82" s="4"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D83" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F83" s="4"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C84" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="D84" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F84" s="4"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C85" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="D85" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C86" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="D86" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C87" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="D87" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C88" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="D88" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C89" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="D89" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C90" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="D90" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C91" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="D91" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F91"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C92" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="D92" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F92"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C93" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="D93" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F93"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D94" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D95" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C96" s="4" t="s">
-        <v>79</v>
-      </c>
+      <c r="C96" s="4"/>
       <c r="D96" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="C97" s="4"/>
       <c r="D97" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G97" s="4"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C98" s="4" t="s">
-        <v>74</v>
-      </c>
+      <c r="C98" s="4"/>
       <c r="D98" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G98" s="4"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C99" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="C99" s="4"/>
       <c r="D99" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D100" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G100" s="4"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D101" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Yorion.xlsx
+++ b/Decks/Yorion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B15C73D-8B15-4371-802B-AF43C84367F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC27B045-5D3A-4383-80E6-F3443089E4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B4381E2-5BD2-4C34-834D-2B6229AFC0E6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="69">
   <si>
     <t>Função</t>
   </si>
@@ -155,9 +155,6 @@
     <t>Flickerwisp</t>
   </si>
   <si>
-    <t>Guardian of Ghirapur</t>
-  </si>
-  <si>
     <t>Mirror of Life Trapping</t>
   </si>
   <si>
@@ -188,9 +185,6 @@
     <t>Vedalken Mastermind</t>
   </si>
   <si>
-    <t>Teleportation Circle</t>
-  </si>
-  <si>
     <t>Airbender Ascension</t>
   </si>
   <si>
@@ -203,36 +197,18 @@
     <t>Mirrormind Crown</t>
   </si>
   <si>
-    <t>Crystal Shard</t>
-  </si>
-  <si>
-    <t>Conjurer's Closet</t>
-  </si>
-  <si>
-    <t>Semester's End</t>
-  </si>
-  <si>
     <t>Proteus Staff</t>
   </si>
   <si>
     <t>Abdel Adrian, Gorion's Ward</t>
   </si>
   <si>
-    <t>Ojutai's Command</t>
-  </si>
-  <si>
     <t>Claim Jumper</t>
   </si>
   <si>
     <t>Salvation Swan</t>
   </si>
   <si>
-    <t>Personify</t>
-  </si>
-  <si>
-    <t>Ellyn Harbreeze, Busybody</t>
-  </si>
-  <si>
     <t>Skycoach Conductor // All Aboard</t>
   </si>
   <si>
@@ -245,10 +221,28 @@
     <t>Anticasual Vestige</t>
   </si>
   <si>
-    <t>Hop to It</t>
-  </si>
-  <si>
     <t>Perplexing Test</t>
+  </si>
+  <si>
+    <t>Glacial Fortress</t>
+  </si>
+  <si>
+    <t>Exotic Orchard</t>
+  </si>
+  <si>
+    <t>Soulherder</t>
+  </si>
+  <si>
+    <t>Quantum Entanglement</t>
+  </si>
+  <si>
+    <t>Mountain</t>
+  </si>
+  <si>
+    <t>Oujutai's Command</t>
+  </si>
+  <si>
+    <t>Azorius Charm</t>
   </si>
 </sst>
 </file>
@@ -693,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -705,10 +699,10 @@
       </c>
       <c r="B4" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -723,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -738,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1293,10 +1287,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D43" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1323,10 +1317,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D45" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1370,10 +1364,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D48" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F48"/>
     </row>
@@ -1383,10 +1377,10 @@
       </c>
       <c r="B49" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="D49" t="s">
         <v>24</v>
@@ -1498,7 +1492,7 @@
         <v>1</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D56" t="s">
         <v>32</v>
@@ -1530,10 +1524,10 @@
         <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D58" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1545,7 +1539,7 @@
         <v>1</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D59" t="s">
         <v>34</v>
@@ -1574,13 +1568,13 @@
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D61" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -1617,588 +1611,596 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>40</v>
+      </c>
+      <c r="B64" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C64" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B64" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="D64" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F64"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" ref="B65:B101" si="1">C65&lt;&gt;D65</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F65"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D66" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F66" s="4"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D67" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F67" s="4"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D68" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B70" s="5" t="b">
         <f>C70&lt;&gt;D70</f>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F70"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D71" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D72" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F72" s="4"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>45</v>
+      </c>
+      <c r="B73" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B73" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="D73" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F73"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D74" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F74"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D75" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F75"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B76" s="5" t="b">
         <f>C76&lt;&gt;D76</f>
         <v>0</v>
       </c>
       <c r="C76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F76"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D77" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E77" s="4"/>
       <c r="F77"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D78" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D79" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D80" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E80" s="4"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D81" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F81" s="4"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D82" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F82" s="4"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D83" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F83" s="4"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D84" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F84" s="4"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D85" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D86" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D87" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D88" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D89" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D90" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D91" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F91"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D92" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F92"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D93" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F93"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D94" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D95" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C96" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="D96" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C97" s="4"/>
+      <c r="C97" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="D97" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G97" s="4"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C98" s="4"/>
+      <c r="C98" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="D98" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G98" s="4"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C99" s="4"/>
+      <c r="C99" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="D99" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D100" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G100" s="4"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D101" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Yorion.xlsx
+++ b/Decks/Yorion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC27B045-5D3A-4383-80E6-F3443089E4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418FEA90-70CE-44CC-B324-61113EEB8911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B4381E2-5BD2-4C34-834D-2B6229AFC0E6}"/>
   </bookViews>
@@ -2131,10 +2131,10 @@
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D97" t="s">
         <v>51</v>
@@ -2147,10 +2147,10 @@
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D98" t="s">
         <v>51</v>
@@ -2163,10 +2163,10 @@
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D99" t="s">
         <v>51</v>
@@ -2178,10 +2178,10 @@
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D100" t="s">
         <v>51</v>
